--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_328_R33.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_328_R33.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.797</v>
+        <v>2.3433</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1358</v>
+        <v>4.0732</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3388</v>
+        <v>-1.7299</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3091</v>
+        <v>0.6775</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8919</v>
+        <v>3.1235</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.201</v>
+        <v>-2.446</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2858</v>
+        <v>2.3463</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4823</v>
+        <v>3.2097</v>
       </c>
       <c r="L2" t="n">
-        <v>1.8034</v>
+        <v>-0.8635</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.5948</v>
+        <v>-1.6687</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5904</v>
+        <v>-0.0862</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.0044</v>
+        <v>-1.5825</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7814</v>
+        <v>0.3822</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0974</v>
+        <v>-0.165</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.5472</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3247</v>
+        <v>0.8197</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0722</v>
+        <v>1.8919</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2525</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7233</v>
+        <v>1.3823</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3524</v>
+        <v>1.9563</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6291</v>
+        <v>-0.574</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6775</v>
+        <v>-0.3091</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1235</v>
+        <v>0.8919</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.446</v>
+        <v>-1.201</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3463</v>
+        <v>3.2858</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2097</v>
+        <v>1.4823</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.8635</v>
+        <v>1.8034</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6687</v>
+        <v>-3.5948</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0862</v>
+        <v>-0.5904</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5825</v>
+        <v>-3.0044</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4639</v>
+        <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7622</v>
+        <v>0.3666</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1142</v>
+        <v>-0.0822</v>
       </c>
       <c r="U3" t="n">
-        <v>0.648</v>
+        <v>0.4488</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8197</v>
+        <v>1.3247</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8919</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6721</v>
+        <v>0.8573</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5211</v>
+        <v>0.639</v>
       </c>
       <c r="F4" t="n">
-        <v>0.151</v>
+        <v>0.2183</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3651</v>
@@ -766,13 +766,13 @@
         <v>0.4639</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1046</v>
+        <v>0.0806</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1195</v>
+        <v>0.1867</v>
       </c>
       <c r="V4" t="n">
         <v>0.6778999999999999</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0121</v>
+        <v>-0.0725</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5515</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5395</v>
+        <v>0.556</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5047</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2905</v>
+        <v>-1.6602</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2142</v>
+        <v>0.7897</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7726</v>
+        <v>-0.2237</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3444</v>
+        <v>-1.4383</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4282</v>
+        <v>1.2146</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2679</v>
+        <v>-0.6468</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0539</v>
+        <v>-0.222</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.214</v>
+        <v>-0.4248</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0435</v>
+        <v>-0.1298</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5975</v>
+        <v>-0.4048</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6409</v>
+        <v>0.275</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3995</v>
+        <v>-0.1485</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8211000000000001</v>
+        <v>0.6262</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4216</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8705000000000001</v>
+        <v>1.5047</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6602</v>
+        <v>1.2905</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7897</v>
+        <v>0.2142</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2237</v>
+        <v>1.7726</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.4383</v>
+        <v>1.3444</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2146</v>
+        <v>0.4282</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6468</v>
+        <v>-0.2679</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.222</v>
+        <v>-0.0539</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4248</v>
+        <v>-0.214</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4569</v>
+        <v>-0.1171</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5975</v>
+        <v>-0.5228</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1406</v>
+        <v>0.4057</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1368</v>
+        <v>-0.9516</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3198</v>
+        <v>-0.2018</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.7498</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8829</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4859</v>
+        <v>-0.3007</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9538</v>
+        <v>-1.2296</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4942</v>
+        <v>0.0956</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4596</v>
+        <v>-1.3252</v>
       </c>
       <c r="G8" t="n">
         <v>0.3045</v>
@@ -1078,13 +1078,13 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6888</v>
+        <v>0.0354</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8136</v>
+        <v>-0.2238</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1248</v>
+        <v>0.2592</v>
       </c>
       <c r="V8" t="n">
         <v>1.214</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9852</v>
+        <v>-2.8591</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2085</v>
+        <v>-1.78</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-1.0791</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2877</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1401</v>
+        <v>0.2662</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6721</v>
+        <v>-0.2436</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8123</v>
+        <v>0.5098</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6778999999999999</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.9074</v>
+        <v>-4.3012</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6452</v>
+        <v>-4.1734</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2622</v>
+        <v>-0.1278</v>
       </c>
       <c r="G10" t="n">
         <v>-4.6958</v>
@@ -1234,13 +1234,13 @@
         <v>2.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2116</v>
+        <v>-0.6054</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.411</v>
+        <v>-0.9392</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1994</v>
+        <v>0.3339</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.164</v>
+        <v>-4.7271</v>
       </c>
       <c r="E11" t="n">
         <v>-3.6602</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5038</v>
+        <v>-1.067</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8868</v>
@@ -1312,13 +1312,13 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9782999999999999</v>
+        <v>-0.5414</v>
       </c>
       <c r="T11" t="n">
         <v>-0.326</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6524</v>
+        <v>-0.2155</v>
       </c>
       <c r="V11" t="n">
         <v>1.8608</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.0135</v>
+        <v>-7.2755</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0393</v>
+        <v>-5.2005</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9742</v>
+        <v>-2.075</v>
       </c>
       <c r="G12" t="n">
         <v>-7.392</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0004</v>
+        <v>-0.2625</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4007</v>
+        <v>-0.5619</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4002</v>
+        <v>0.2994</v>
       </c>
       <c r="V12" t="n">
         <v>2.0026</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.3557</v>
+        <v>-16.9822</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.6275</v>
+        <v>-8.254100000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.728299999999999</v>
+        <v>-8.728200000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-18.2032</v>
@@ -1459,7 +1459,7 @@
         <v>-16.8787</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.639100000000001</v>
+        <v>-4.639099999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-18.5562</v>
@@ -1468,13 +1468,13 @@
         <v>13.9171</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1993</v>
+        <v>-0.8259000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.2042</v>
+        <v>-3.8309</v>
       </c>
       <c r="U13" t="n">
-        <v>3.004799999999999</v>
+        <v>3.005</v>
       </c>
       <c r="V13" t="n">
         <v>6.685700000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.220800000000001</v>
+        <v>8.9069</v>
       </c>
       <c r="E14" t="n">
-        <v>6.4619</v>
+        <v>6.226</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7589</v>
+        <v>2.6809</v>
       </c>
       <c r="G14" t="n">
         <v>4.5428</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8377</v>
+        <v>0.5239</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1845</v>
+        <v>-0.4204</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0223</v>
+        <v>0.9443</v>
       </c>
       <c r="V14" t="n">
         <v>2.6805</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5819</v>
+        <v>4.2509</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6463</v>
+        <v>1.2924</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9357</v>
+        <v>2.9585</v>
       </c>
       <c r="G15" t="n">
         <v>2.8031</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7635</v>
+        <v>0.4325</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0474</v>
+        <v>-0.3064</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7161</v>
+        <v>0.7389</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7195</v>
+        <v>3.7417</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0112</v>
+        <v>0.7753</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7083</v>
+        <v>2.9664</v>
       </c>
       <c r="G16" t="n">
         <v>2.7809</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0474</v>
+        <v>-0.1885</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4995</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5361</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FAYE</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9904</v>
+        <v>2.3742</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6086</v>
+        <v>1.3708</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3817</v>
+        <v>1.0033</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1941</v>
+        <v>3.0879</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4585</v>
+        <v>0.1069</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6526</v>
+        <v>2.9811</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5454</v>
+        <v>1.9052</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6253</v>
+        <v>0.3396</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9201</v>
+        <v>1.5657</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3513</v>
+        <v>1.1827</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0838</v>
+        <v>-0.2327</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2676</v>
+        <v>1.4154</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8685</v>
+        <v>-0.1208</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5272</v>
+        <v>-0.5344</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3413</v>
+        <v>0.4136</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>L. CAVALIERE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4262</v>
+        <v>1.6992</v>
       </c>
       <c r="E18" t="n">
-        <v>1.017</v>
+        <v>-0.795</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4092</v>
+        <v>2.4942</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0879</v>
+        <v>0.9427</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1069</v>
+        <v>-0.2017</v>
       </c>
       <c r="I18" t="n">
-        <v>2.9811</v>
+        <v>1.1443</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9052</v>
+        <v>0.4534</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3396</v>
+        <v>0.3564</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5657</v>
+        <v>0.097</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1827</v>
+        <v>0.4893</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2327</v>
+        <v>-0.5581</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4154</v>
+        <v>1.0474</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0688</v>
+        <v>0.2978</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8883</v>
+        <v>-0.4597</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1805</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.6805</v>
+        <v>-1.8608</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. CAVALIERE</t>
+          <t>M. FAYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0873</v>
+        <v>1.2998</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1489</v>
+        <v>1.0189</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2361</v>
+        <v>0.2809</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9427</v>
+        <v>0.1941</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2017</v>
+        <v>-0.4585</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1443</v>
+        <v>0.6526</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4534</v>
+        <v>1.5454</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3564</v>
+        <v>0.6253</v>
       </c>
       <c r="L19" t="n">
-        <v>0.097</v>
+        <v>0.9201</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4893</v>
+        <v>-1.3513</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5581</v>
+        <v>-1.0838</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0474</v>
+        <v>-0.2676</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3141</v>
+        <v>0.1779</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8136</v>
+        <v>-0.0626</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4995</v>
+        <v>0.2405</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8608</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RHODEN</t>
+          <t>Y. OUATTARA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5668</v>
+        <v>0.2884</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5725</v>
+        <v>1.2932</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0057</v>
+        <v>-1.0049</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1544</v>
+        <v>3.2253</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7959000000000001</v>
+        <v>-0.4753</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9503</v>
+        <v>3.7006</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1538</v>
+        <v>4.5443</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3647</v>
+        <v>0.1043</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2109</v>
+        <v>4.44</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3082</v>
+        <v>-1.319</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5688</v>
+        <v>-0.5796</v>
       </c>
       <c r="O20" t="n">
         <v>-0.7393999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.6237</v>
+        <v>-2.7834</v>
       </c>
       <c r="R20" t="n">
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>1.4892</v>
+        <v>-0.3312</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9006</v>
+        <v>-0.4676</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5887</v>
+        <v>0.1364</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0028</v>
+        <v>-0.1544</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1437</v>
+        <v>0.0257</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1465</v>
+        <v>-0.1801</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1456</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6067</v>
+        <v>0.4551</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0395</v>
+        <v>-0.0784</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5671</v>
+        <v>0.5335</v>
       </c>
       <c r="V21" t="n">
         <v>0.5361</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y. OUATTARA</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0319</v>
+        <v>-0.1928</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9394</v>
+        <v>-0.1936</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9712</v>
+        <v>0.0009</v>
       </c>
       <c r="G22" t="n">
-        <v>3.2253</v>
+        <v>-0.6718</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4753</v>
+        <v>-1.0229</v>
       </c>
       <c r="I22" t="n">
-        <v>3.7006</v>
+        <v>0.3511</v>
       </c>
       <c r="J22" t="n">
-        <v>4.5443</v>
+        <v>0.6795</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1043</v>
+        <v>0.0609</v>
       </c>
       <c r="L22" t="n">
-        <v>4.44</v>
+        <v>0.6186</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.319</v>
+        <v>-1.3513</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5796</v>
+        <v>-1.0838</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.2676</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7834</v>
+        <v>-0.4639</v>
       </c>
       <c r="R22" t="n">
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6515</v>
+        <v>-0.338</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8215</v>
+        <v>-0.2985</v>
       </c>
       <c r="U22" t="n">
-        <v>0.17</v>
+        <v>-0.0395</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.214</v>
+        <v>-0.1107</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.1107</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>J. RHODEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1858</v>
+        <v>-0.4605</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7834</v>
+        <v>-0.2532</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4024</v>
+        <v>-0.2074</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6718</v>
+        <v>-0.1544</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0229</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3511</v>
+        <v>-0.9503</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6795</v>
+        <v>1.1538</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0609</v>
+        <v>1.3647</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6186</v>
+        <v>-0.2109</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3513</v>
+        <v>-1.3082</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0838</v>
+        <v>-0.5688</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2676</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="R23" t="n">
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3311</v>
+        <v>0.4619</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8883</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4428</v>
+        <v>0.387</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1107</v>
+        <v>-0.5361</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1107</v>
+        <v>0.1418</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.1877</v>
+        <v>-0.9512</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5441</v>
+        <v>1.0159</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7319</v>
+        <v>-1.9671</v>
       </c>
       <c r="G24" t="n">
         <v>3.0703</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4204</v>
+        <v>-0.1838</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6721</v>
+        <v>-0.2003</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2517</v>
+        <v>0.0165</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7501</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8289</v>
+        <v>-2.6602</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3539</v>
+        <v>-2.118</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.475</v>
+        <v>-0.5422</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4721</v>
@@ -2404,13 +2404,13 @@
         <v>0.232</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1274</v>
+        <v>0.0413</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2987</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1713</v>
+        <v>0.1041</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1418</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>17.3558</v>
+        <v>18.142</v>
       </c>
       <c r="E26" t="n">
-        <v>9.6585</v>
+        <v>9.6584</v>
       </c>
       <c r="F26" t="n">
-        <v>7.697200000000002</v>
+        <v>8.483400000000001</v>
       </c>
       <c r="G26" t="n">
         <v>18.2032</v>
@@ -2467,13 +2467,13 @@
         <v>-4.31</v>
       </c>
       <c r="N26" t="n">
-        <v>-8.209200000000001</v>
+        <v>-8.209199999999999</v>
       </c>
       <c r="O26" t="n">
         <v>3.899</v>
       </c>
       <c r="P26" t="n">
-        <v>4.638999999999998</v>
+        <v>4.639000000000001</v>
       </c>
       <c r="Q26" t="n">
         <v>-13.9172</v>
@@ -2482,16 +2482,16 @@
         <v>18.5562</v>
       </c>
       <c r="S26" t="n">
-        <v>1.1992</v>
+        <v>1.9857</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.0049</v>
+        <v>-3.0047</v>
       </c>
       <c r="U26" t="n">
-        <v>4.2042</v>
+        <v>4.990499999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>-6.685699999999999</v>
+        <v>-6.6857</v>
       </c>
       <c r="W26" t="n">
         <v>4.067400000000001</v>
